--- a/workspace/framework_paper/edf/edf-25/edf-25_schedulables.xlsx
+++ b/workspace/framework_paper/edf/edf-25/edf-25_schedulables.xlsx
@@ -486,7 +486,7 @@
         <v>50</v>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -500,7 +500,7 @@
         <v>50</v>
       </c>
       <c r="D6" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -514,7 +514,7 @@
         <v>49</v>
       </c>
       <c r="D7" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -528,7 +528,7 @@
         <v>49</v>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         <v>47</v>
       </c>
       <c r="D9" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -556,7 +556,7 @@
         <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -570,7 +570,7 @@
         <v>35</v>
       </c>
       <c r="D11" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         <v>27</v>
       </c>
       <c r="D12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -598,7 +598,7 @@
         <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -612,7 +612,7 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -654,7 +654,7 @@
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -668,7 +668,7 @@
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -682,7 +682,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">

--- a/workspace/framework_paper/edf/edf-25/edf-25_schedulables.xlsx
+++ b/workspace/framework_paper/edf/edf-25/edf-25_schedulables.xlsx
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -710,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
